--- a/Data/EC/NIT-9009033021.xlsx
+++ b/Data/EC/NIT-9009033021.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4DFEB37-0907-45B5-AB1C-3C52C534D060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{55572E3F-3CF6-470B-A81A-A5105B8D20E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{957EC086-8EF4-4D25-92CB-96C9125AE04C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{69B5697B-65D1-4963-9131-83BDC5DA9494}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -422,22 +422,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{199200BD-832A-4B9C-656C-0A7C33EE1679}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEE105AE-81C0-6BF9-B9CA-82D6DCFA4CD1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -446,7 +446,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -459,7 +459,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -788,23 +788,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7CB1930-5941-4D7B-A346-DF36094F0627}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2D21FE3-F6CA-4DE3-9BEA-AF74443796D8}">
   <dimension ref="B2:J22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="22"/>
       <c r="D2" s="23" t="s">
@@ -817,7 +817,7 @@
       <c r="I2" s="23"/>
       <c r="J2" s="23"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="22"/>
       <c r="D3" s="24"/>
@@ -828,7 +828,7 @@
       <c r="I3" s="24"/>
       <c r="J3" s="24"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="22"/>
       <c r="D4" s="24"/>
@@ -839,7 +839,7 @@
       <c r="I4" s="24"/>
       <c r="J4" s="24"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="22"/>
       <c r="D5" s="25"/>
@@ -850,8 +850,8 @@
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
@@ -866,8 +866,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -882,8 +882,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>14</v>
       </c>
@@ -898,8 +898,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>15</v>
       </c>
@@ -918,7 +918,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -947,7 +947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -970,7 +970,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="26" t="s">
         <v>21</v>
       </c>
@@ -981,7 +981,7 @@
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="26" t="s">
         <v>20</v>
       </c>
